--- a/OUTPUT/direct_P23836_Escherichia_coli_str__K-12_substr__W3110.xlsx
+++ b/OUTPUT/direct_P23836_Escherichia_coli_str__K-12_substr__W3110.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.0028</v>
+        <v>0.002998800479808077</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.403</v>
+        <v>0.4030387844862055</v>
       </c>
     </row>
     <row r="4">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.403</v>
+        <v>0.4030387844862055</v>
       </c>
     </row>
     <row r="5">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.878</v>
+        <v>0.8778488604558177</v>
       </c>
     </row>
     <row r="6">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8698</v>
+        <v>0.8696521391443423</v>
       </c>
     </row>
   </sheetData>
